--- a/data/dividends_info_20260829.xlsx
+++ b/data/dividends_info_20260829.xlsx
@@ -3368,7 +3368,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3385,7 +3385,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3395,14 +3395,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3419,7 +3419,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3470,7 +3470,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3480,14 +3480,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3504,7 +3504,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3538,7 +3538,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3572,7 +3572,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3582,14 +3582,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3623,7 +3623,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3640,7 +3640,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3650,14 +3650,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3674,7 +3674,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3708,7 +3708,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3742,7 +3742,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3759,7 +3759,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3776,7 +3776,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3793,7 +3793,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3810,7 +3810,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3820,14 +3820,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3844,7 +3844,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3878,7 +3878,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3929,7 +3929,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3939,14 +3939,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3963,7 +3963,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3980,7 +3980,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3997,7 +3997,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4007,14 +4007,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4031,7 +4031,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4048,7 +4048,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4058,14 +4058,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4082,7 +4082,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4099,7 +4099,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4116,7 +4116,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4133,7 +4133,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4167,7 +4167,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4184,7 +4184,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4201,7 +4201,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4211,14 +4211,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4228,14 +4228,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4245,14 +4245,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4269,7 +4269,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4286,7 +4286,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4303,7 +4303,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4313,14 +4313,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Guidotti Ships S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4337,7 +4337,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4347,14 +4347,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4371,7 +4371,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4388,7 +4388,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4405,7 +4405,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4422,7 +4422,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4439,7 +4439,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4456,7 +4456,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4473,7 +4473,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4490,7 +4490,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4507,7 +4507,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4524,7 +4524,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4541,7 +4541,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Guidotti Ships S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4551,14 +4551,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4568,14 +4568,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4585,14 +4585,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4609,7 +4609,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4664,673 +4664,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AEFFE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AEFFE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ambromobiliare S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CIRCLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DBA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Energy S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Estrima S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FRENDY ENERGY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Farmacosmo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Guidotti Ships S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Haiki+ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>INNOVATEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Markbass S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Nusco S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PREMIA FINANCE S.P.A</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Redelfi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Simone S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>T.P.S. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TMP Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Tecno S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Telmes S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TradeLab S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Triboo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>WEBSOLUTE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>YOLO GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ZEST S.p.A.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>